--- a/public/residuedefinition.xlsx
+++ b/public/residuedefinition.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\myweb\tmdi_20260520\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A46EFB1A-489E-4FAF-9CA5-B37EAB08F207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4633BE53-3A07-4DED-9607-C82487BD3762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E699E50F-BA78-405A-B155-F982B11DCCA9}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E699E50F-BA78-405A-B155-F982B11DCCA9}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
